--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R6d2f01d89ce3433d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R84f2122c2ca84b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rd1bd115215104b74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R7717c200da6a4891"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R18a243dc583c4c0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Ra6fa6356f4f94495"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rd7fd6c06b52c4628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R170410dfaf0c4bdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Ref5ee17b80cd4fdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R7874929d41e343d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -860,31 +860,17 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="32" t="str">
+      <x:c r="A6" s="35" t="str">
         <x:v>primary_reasons</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="str">
+      <x:c r="B6" s="36" t="str">
         <x:v>missing_segment,missing_profile,ladder_not_increasing</x:v>
       </x:c>
-      <x:c r="C6" s="33" t="str">
+      <x:c r="C6" s="36" t="str">
         <x:v>按资产逐项对应</x:v>
       </x:c>
-      <x:c r="D6" s="34" t="str">
+      <x:c r="D6" s="37" t="str">
         <x:v>requeue_reason_order与输入问题</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="78" customHeight="1">
-      <x:c r="A7" s="35" t="str">
-        <x:v>reference_members</x:v>
-      </x:c>
-      <x:c r="B7" s="36" t="str">
-        <x:v>src/audit_hls_publish.mjs,reports/asset_publish_matrix.csv,reports/variant_playlist_audit.csv,reports/segment_requeue.csv,reports/bandwidth_ladder.csv</x:v>
-      </x:c>
-      <x:c r="C7" s="36" t="str">
-        <x:v>相对路径逐字匹配</x:v>
-      </x:c>
-      <x:c r="D7" s="37" t="str">
-        <x:v>reference.zip成员</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
